--- a/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:28:51+00:00</t>
+    <t>2026-09-15T08:26:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
